--- a/AAII_Financials/Quarterly/RGC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="92">
   <si>
     <t>RGC</t>
   </si>
@@ -1231,10 +1231,10 @@
         <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>100</v>
@@ -1482,11 +1482,11 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F20" s="3">
         <v>100</v>
@@ -1494,11 +1494,11 @@
       <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-100</v>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J20" s="3">
         <v>100</v>
@@ -1566,10 +1566,10 @@
         <v>-900</v>
       </c>
       <c r="H21" s="3">
-        <v>-900</v>
+        <v>-1000</v>
       </c>
       <c r="I21" s="3">
-        <v>-900</v>
+        <v>-1000</v>
       </c>
       <c r="J21" s="3">
         <v>-1200</v>
@@ -2334,11 +2334,11 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F32" s="3">
         <v>-100</v>
@@ -2346,11 +2346,11 @@
       <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>100</v>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J32" s="3">
         <v>-100</v>
@@ -5417,11 +5417,11 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>3</v>
